--- a/data/trans_orig/P36BPD04_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023</t>
+          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33189</t>
+          <t>37164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>15610</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>31281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57457</t>
+          <t>59612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83044</t>
+          <t>80774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118796</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54627</t>
+          <t>54743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82789</t>
+          <t>83016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143437</t>
+          <t>144047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>188583</t>
+          <t>191197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>267091</t>
+          <t>267888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311647</t>
+          <t>313549</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>240174</t>
+          <t>238160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274170</t>
+          <t>274638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>517991</t>
+          <t>515457</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>576380</t>
+          <t>574815</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78022</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113732</t>
+          <t>113043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86080</t>
+          <t>87081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115570</t>
+          <t>116177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>175155</t>
+          <t>174343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220433</t>
+          <t>220661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45261</t>
+          <t>46797</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36818</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40487</t>
+          <t>41283</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72674</t>
+          <t>74133</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63663</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99741</t>
+          <t>98876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51065</t>
+          <t>50986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76384</t>
+          <t>76648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123692</t>
+          <t>124086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164632</t>
+          <t>166584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>236354</t>
+          <t>235824</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280950</t>
+          <t>278804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193710</t>
+          <t>193393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>228140</t>
+          <t>227258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>443493</t>
+          <t>439145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>497190</t>
+          <t>496728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68679</t>
+          <t>68040</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102268</t>
+          <t>100468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>70182</t>
+          <t>69649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>95916</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>146063</t>
+          <t>145066</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189299</t>
+          <t>187378</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43545</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50188</t>
+          <t>48050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>33248</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>138361</t>
+          <t>139661</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>30972</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>47311</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156079</t>
+          <t>156746</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>349935</t>
+          <t>344145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>602840</t>
+          <t>586856</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77249</t>
+          <t>76493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97848</t>
+          <t>96676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>432253</t>
+          <t>432388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>720724</t>
+          <t>704096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>34285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147371</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41322</t>
+          <t>41535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61262</t>
+          <t>61744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57093</t>
+          <t>64735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206853</t>
+          <t>207905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>59582</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116790</t>
+          <t>111351</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56581</t>
+          <t>56568</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>611529</t>
+          <t>608641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130913</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>862066</t>
+          <t>823559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153642</t>
+          <t>153780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207067</t>
+          <t>207441</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60830</t>
+          <t>60253</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166436</t>
+          <t>165910</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>206958</t>
+          <t>208071</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>355273</t>
+          <t>352077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>531872</t>
+          <t>530451</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>605025</t>
+          <t>602822</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>228465</t>
+          <t>224940</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>572992</t>
+          <t>575760</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>682848</t>
+          <t>713031</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1146226</t>
+          <t>1140300</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183420</t>
+          <t>182962</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>237909</t>
+          <t>238022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80607</t>
+          <t>77056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197919</t>
+          <t>199117</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250515</t>
+          <t>252438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>415252</t>
+          <t>415758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22822</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46892</t>
+          <t>49565</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25866</t>
+          <t>25429</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48892</t>
+          <t>50250</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>53156</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87907</t>
+          <t>90914</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77568</t>
+          <t>77769</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116748</t>
+          <t>116624</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85488</t>
+          <t>85313</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135513</t>
+          <t>136663</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166612</t>
+          <t>167711</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240114</t>
+          <t>239542</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>239843</t>
+          <t>238502</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>285955</t>
+          <t>283918</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>462136</t>
+          <t>464718</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>599472</t>
+          <t>600495</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>720357</t>
+          <t>721815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>867025</t>
+          <t>867544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>68216</t>
+          <t>67414</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>105246</t>
+          <t>104360</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>130280</t>
+          <t>129042</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>262857</t>
+          <t>252389</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>210028</t>
+          <t>211113</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>344413</t>
+          <t>348046</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28477</t>
+          <t>29404</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>26724</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>57862</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33682</t>
+          <t>32196</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71868</t>
+          <t>71048</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84264</t>
+          <t>83140</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103368</t>
+          <t>100609</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>142271</t>
+          <t>140349</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>149607</t>
+          <t>148510</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>209414</t>
+          <t>207915</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>104198</t>
+          <t>103744</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>153690</t>
+          <t>158660</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>440804</t>
+          <t>439693</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>488710</t>
+          <t>492211</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>555527</t>
+          <t>559764</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>630390</t>
+          <t>632560</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25429</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>70985</t>
+          <t>69920</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>121040</t>
+          <t>120786</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>160662</t>
+          <t>161109</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>154536</t>
+          <t>155272</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>216596</t>
+          <t>215692</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>152968</t>
+          <t>148613</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>238857</t>
+          <t>237241</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>177139</t>
+          <t>172219</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1001101</t>
+          <t>975885</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>361537</t>
+          <t>364797</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1287973</t>
+          <t>1264639</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>464171</t>
+          <t>479188</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>663534</t>
+          <t>656549</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>419643</t>
+          <t>422088</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>569314</t>
+          <t>567200</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>951175</t>
+          <t>953567</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1198504</t>
+          <t>1207502</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1849280</t>
+          <t>1847736</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2310499</t>
+          <t>2249497</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1619371</t>
+          <t>1631001</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2138233</t>
+          <t>2150504</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3651685</t>
+          <t>3581516</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4278006</t>
+          <t>4260892</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,31%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>479528</t>
+          <t>483556</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>678322</t>
+          <t>679496</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>565265</t>
+          <t>573379</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>782486</t>
+          <t>782876</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1119265</t>
+          <t>1129780</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1421222</t>
+          <t>1430669</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD04_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20241</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>25935</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15610</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>37901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42018</t>
+          <t>45332</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31281</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59612</t>
+          <t>62640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>98548</t>
+          <t>103974</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80774</t>
+          <t>85959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118491</t>
+          <t>125380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67298</t>
+          <t>70355</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>56518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83016</t>
+          <t>85231</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>165846</t>
+          <t>174329</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144047</t>
+          <t>149884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>191197</t>
+          <t>198941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>290785</t>
+          <t>320653</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>267888</t>
+          <t>297587</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>313549</t>
+          <t>348295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>257388</t>
+          <t>279142</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>238160</t>
+          <t>260064</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274638</t>
+          <t>298677</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>548172</t>
+          <t>599795</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>515457</t>
+          <t>567837</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>574815</t>
+          <t>627084</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,35%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95638</t>
+          <t>106594</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79506</t>
+          <t>89177</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113043</t>
+          <t>127316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>101005</t>
+          <t>112979</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87081</t>
+          <t>96079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116177</t>
+          <t>129005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>196643</t>
+          <t>219574</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174343</t>
+          <t>196130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220661</t>
+          <t>246774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29384</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19934</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46797</t>
+          <t>45324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36769</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>54858</t>
+          <t>57548</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41283</t>
+          <t>42678</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>74133</t>
+          <t>77801</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80128</t>
+          <t>79794</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63686</t>
+          <t>64467</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98876</t>
+          <t>98601</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64055</t>
+          <t>66472</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50986</t>
+          <t>53677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76648</t>
+          <t>79861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>144183</t>
+          <t>146266</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124086</t>
+          <t>124259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166584</t>
+          <t>168339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>259126</t>
+          <t>278921</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>235824</t>
+          <t>253135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278804</t>
+          <t>298828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>210364</t>
+          <t>237880</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193393</t>
+          <t>219482</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227258</t>
+          <t>255106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>469490</t>
+          <t>516800</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>439145</t>
+          <t>489635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>496728</t>
+          <t>548173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>60,48%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83576</t>
+          <t>93801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68040</t>
+          <t>77865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100468</t>
+          <t>113775</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82687</t>
+          <t>91940</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69649</t>
+          <t>77993</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95916</t>
+          <t>107857</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>166262</t>
+          <t>185741</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145066</t>
+          <t>162939</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>187378</t>
+          <t>209720</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25136</t>
+          <t>26848</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46079</t>
+          <t>37898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>3,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,67 +1898,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>32945</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>22680</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>46542</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>30855</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>11085</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>48050</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82441</t>
+          <t>83019</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33248</t>
+          <t>66627</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>139661</t>
+          <t>101215</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>19414</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>35206</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>105335</t>
+          <t>109952</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>90780</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156746</t>
+          <t>128544</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>470512</t>
+          <t>251261</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>344145</t>
+          <t>227435</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>586856</t>
+          <t>271860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>87244</t>
+          <t>97428</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76493</t>
+          <t>86044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96676</t>
+          <t>108782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>557756</t>
+          <t>348689</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>432388</t>
+          <t>324409</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>704096</t>
+          <t>374842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>90175</t>
+          <t>110484</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34285</t>
+          <t>92536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152491</t>
+          <t>133664</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50489</t>
+          <t>56471</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41535</t>
+          <t>47081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61744</t>
+          <t>67963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>140664</t>
+          <t>166955</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64735</t>
+          <t>145127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207905</t>
+          <t>191500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>77575</t>
+          <t>75618</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>57589</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111351</t>
+          <t>95813</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>253113</t>
+          <t>55584</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56568</t>
+          <t>43864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>608641</t>
+          <t>71314</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>330688</t>
+          <t>131202</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>110752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>823559</t>
+          <t>157165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>179199</t>
+          <t>200817</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153780</t>
+          <t>175411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207441</t>
+          <t>232879</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>125498</t>
+          <t>139395</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60253</t>
+          <t>120125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>165910</t>
+          <t>157544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>304697</t>
+          <t>340211</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>208071</t>
+          <t>305324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>352077</t>
+          <t>373718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>567622</t>
+          <t>614476</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>530451</t>
+          <t>576908</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>602822</t>
+          <t>648904</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>447960</t>
+          <t>497476</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>224940</t>
+          <t>473489</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>575760</t>
+          <t>522664</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1015581</t>
+          <t>1111952</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>713031</t>
+          <t>1064855</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1140300</t>
+          <t>1153841</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>210260</t>
+          <t>239815</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182962</t>
+          <t>210552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>238022</t>
+          <t>274300</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>150411</t>
+          <t>167625</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77056</t>
+          <t>146643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199117</t>
+          <t>185931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>360671</t>
+          <t>407440</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252438</t>
+          <t>371242</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>415758</t>
+          <t>444968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034655</t>
+          <t>1130725</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034655</t>
+          <t>1130725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034655</t>
+          <t>1130725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>976982</t>
+          <t>860080</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>976982</t>
+          <t>860080</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>976982</t>
+          <t>860080</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2011637</t>
+          <t>1990805</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2011637</t>
+          <t>1990805</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2011637</t>
+          <t>1990805</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33178</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>26845</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49565</t>
+          <t>54028</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36073</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25429</t>
+          <t>31155</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50250</t>
+          <t>52742</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>69252</t>
+          <t>79573</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>64584</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90914</t>
+          <t>101241</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>94658</t>
+          <t>104537</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77769</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116624</t>
+          <t>125625</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>114675</t>
+          <t>124884</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85313</t>
+          <t>107117</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>136663</t>
+          <t>143795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>209334</t>
+          <t>229421</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167711</t>
+          <t>204266</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>239542</t>
+          <t>260195</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>261436</t>
+          <t>311553</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>238502</t>
+          <t>284773</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>283918</t>
+          <t>336103</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>517674</t>
+          <t>507836</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>464718</t>
+          <t>484848</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>600495</t>
+          <t>532601</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>779110</t>
+          <t>819389</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>721815</t>
+          <t>783077</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>867544</t>
+          <t>856041</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>61,27%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>84744</t>
+          <t>112521</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>67414</t>
+          <t>92312</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>104360</t>
+          <t>137485</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>172382</t>
+          <t>156283</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>129042</t>
+          <t>137086</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>252389</t>
+          <t>175197</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>257126</t>
+          <t>268805</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>211113</t>
+          <t>241779</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>348046</t>
+          <t>300568</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>840805</t>
+          <t>830306</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>840805</t>
+          <t>830306</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>840805</t>
+          <t>830306</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1314821</t>
+          <t>1397188</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1314821</t>
+          <t>1397188</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1314821</t>
+          <t>1397188</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29404</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>36906</t>
+          <t>37476</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26724</t>
+          <t>26655</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>56079</t>
+          <t>52747</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>47245</t>
+          <t>48300</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32196</t>
+          <t>34770</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71048</t>
+          <t>67562</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>48708</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>31291</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>83140</t>
+          <t>69416</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>119478</t>
+          <t>128126</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100609</t>
+          <t>109383</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>140349</t>
+          <t>150496</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>176385</t>
+          <t>176834</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>148510</t>
+          <t>149054</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>207915</t>
+          <t>206975</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>129681</t>
+          <t>131263</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>103744</t>
+          <t>109663</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>158660</t>
+          <t>153382</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>465394</t>
+          <t>522488</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>439693</t>
+          <t>492768</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>492211</t>
+          <t>549638</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>595075</t>
+          <t>653751</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>559764</t>
+          <t>619186</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>632560</t>
+          <t>693676</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>43580</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25944</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>69920</t>
+          <t>70495</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>139201</t>
+          <t>155790</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>120786</t>
+          <t>134385</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>161109</t>
+          <t>178309</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>182781</t>
+          <t>202223</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>155272</t>
+          <t>173636</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>215692</t>
+          <t>235911</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>760979</t>
+          <t>843881</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>760979</t>
+          <t>843881</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>760979</t>
+          <t>843881</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001486</t>
+          <t>1081109</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001486</t>
+          <t>1081109</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001486</t>
+          <t>1081109</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>195853</t>
+          <t>201656</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>148613</t>
+          <t>169174</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>237241</t>
+          <t>236667</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>379062</t>
+          <t>193245</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>172219</t>
+          <t>168632</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>975885</t>
+          <t>220519</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>574915</t>
+          <t>394900</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>364797</t>
+          <t>355780</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1264639</t>
+          <t>436343</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>591882</t>
+          <t>620849</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>479188</t>
+          <t>574874</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>656549</t>
+          <t>670908</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>513899</t>
+          <t>556165</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>422088</t>
+          <t>519390</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>567200</t>
+          <t>598750</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1105781</t>
+          <t>1177013</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>953567</t>
+          <t>1117928</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1207502</t>
+          <t>1237975</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1979160</t>
+          <t>1908125</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1847736</t>
+          <t>1840559</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2249497</t>
+          <t>1976330</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1986024</t>
+          <t>2142251</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1631001</t>
+          <t>2090858</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2150504</t>
+          <t>2194170</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3965184</t>
+          <t>4050376</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3581516</t>
+          <t>3975343</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4260892</t>
+          <t>4133221</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>607972</t>
+          <t>709647</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>483556</t>
+          <t>659019</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>679496</t>
+          <t>768881</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>696174</t>
+          <t>741090</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>573379</t>
+          <t>699210</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>782876</t>
+          <t>787683</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1304146</t>
+          <t>1450737</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1129780</t>
+          <t>1381407</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1430669</t>
+          <t>1519829</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3374867</t>
+          <t>3440276</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3374867</t>
+          <t>3440276</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3374867</t>
+          <t>3440276</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3575158</t>
+          <t>3632750</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3575158</t>
+          <t>3632750</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3575158</t>
+          <t>3632750</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6950026</t>
+          <t>7073026</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6950026</t>
+          <t>7073026</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6950026</t>
+          <t>7073026</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
